--- a/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
+++ b/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_mexico/ssp_modeling/cost-benefits/cb_config_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tony/Documents/sisepuede_modeling/ssp_bulgaria/ssp_modeling/cost-benefits/cb_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B22CFD6-8403-6446-8AEC-6FA847864C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F59993-5565-C74E-AD41-546D3286E593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-40960" yWindow="-5400" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19780" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -17001,7 +17001,7 @@
         <v>462</v>
       </c>
       <c r="C17">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D17" t="s">
         <v>589</v>

--- a/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
+++ b/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tony/Documents/sisepuede_modeling/ssp_bulgaria/ssp_modeling/cost-benefits/cb_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C8120B7-BBE4-E045-A741-532229B2D4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA9959B-E740-1B4B-B783-5192A767FA8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5920" yWindow="620" windowWidth="27500" windowHeight="19660" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5920" yWindow="620" windowWidth="27500" windowHeight="19660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -6296,7 +6296,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6339,6 +6339,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -6371,7 +6377,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -6383,6 +6389,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -16573,117 +16580,117 @@
         <v>443</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="6">
         <v>-6.5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="6" t="s">
         <v>584</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="6">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="G2" t="b">
+      <c r="G2" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="6" t="s">
         <v>598</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="6" t="s">
         <v>687</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="6" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="C3">
-        <v>-68.099999999999994</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="6">
+        <v>-102.1</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>584</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E3" s="6">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="G3" t="b">
+      <c r="G3" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="6" t="s">
         <v>599</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="6" t="s">
         <v>687</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="6" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="C4">
-        <v>-102.1</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="9">
+        <v>-75.099999999999994</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>584</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E4" s="9">
+        <v>1</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="G4" t="b">
+      <c r="G4" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="9" t="s">
         <v>600</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="9" t="s">
         <v>687</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="9" t="s">
         <v>690</v>
       </c>
     </row>
@@ -16725,79 +16732,79 @@
         <v>690</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="6" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="7" t="s">
         <v>448</v>
       </c>
       <c r="C6">
-        <v>-34.1</v>
-      </c>
-      <c r="D6" t="s">
+        <v>-102.1</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>584</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="G6" t="b">
+      <c r="G6" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="7" t="s">
         <v>601</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="7" t="s">
         <v>687</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="7" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="7" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="6" t="s">
         <v>449</v>
       </c>
       <c r="C7">
-        <v>-66.2</v>
-      </c>
-      <c r="D7" t="s">
+        <v>-41.2</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>584</v>
       </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="G7" t="b">
+      <c r="G7" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="6" t="s">
         <v>602</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="6" t="s">
         <v>687</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="6" t="s">
         <v>690</v>
       </c>
     </row>

--- a/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
+++ b/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tony/Documents/sisepuede_modeling/ssp_bulgaria/ssp_modeling/cost-benefits/cb_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA9959B-E740-1B4B-B783-5192A767FA8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC5D005-B545-884F-BA1C-4014CF80871F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5920" yWindow="620" windowWidth="27500" windowHeight="19660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1480" yWindow="660" windowWidth="27500" windowHeight="17660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -2749,9 +2749,6 @@
     <t>Cost of CCS (plastics)</t>
   </si>
   <si>
-    <t>$40/tonne</t>
-  </si>
-  <si>
     <t>$100/tonne</t>
   </si>
   <si>
@@ -6259,6 +6256,9 @@
   </si>
   <si>
     <t>emission_co2e_ch4_lsmm_anaerobic_*</t>
+  </si>
+  <si>
+    <t>$60/tonne</t>
   </si>
 </sst>
 </file>
@@ -6296,7 +6296,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6341,7 +6341,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6377,7 +6383,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -6390,6 +6396,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9818,7 +9827,7 @@
     </row>
     <row r="184" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A184" s="7" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B184" s="7" t="s">
         <v>329</v>
@@ -10243,10 +10252,10 @@
     </row>
     <row r="209" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A209" s="7" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="C209" s="7" t="s">
         <v>351</v>
@@ -10260,10 +10269,10 @@
     </row>
     <row r="210" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A210" s="7" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="C210" s="7" t="s">
         <v>351</v>
@@ -10277,10 +10286,10 @@
     </row>
     <row r="211" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A211" s="7" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="C211" s="7" t="s">
         <v>351</v>
@@ -10294,13 +10303,13 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" s="8" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="E212" s="7" t="s">
         <v>435</v>
@@ -10308,13 +10317,13 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" s="8" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="B213" s="7" t="s">
+        <v>2055</v>
+      </c>
+      <c r="C213" s="7" t="s">
         <v>2056</v>
-      </c>
-      <c r="C213" s="7" t="s">
-        <v>2057</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>435</v>
@@ -10343,10 +10352,10 @@
         <v>849</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1003</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -10666,10 +10675,10 @@
         <v>843</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1005</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -10791,7 +10800,7 @@
         <v>843</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -10886,7 +10895,7 @@
         <v>881</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -11200,122 +11209,122 @@
         <v>436</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B2" t="s">
         <v>450</v>
       </c>
       <c r="C2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B3" t="s">
         <v>450</v>
       </c>
       <c r="C3" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B4" t="s">
         <v>445</v>
       </c>
       <c r="C4" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B5" t="s">
         <v>444</v>
       </c>
       <c r="C5" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B6" t="s">
         <v>450</v>
       </c>
       <c r="C6" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B7" t="s">
         <v>450</v>
       </c>
       <c r="C7" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B8" t="s">
         <v>450</v>
       </c>
       <c r="C8" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B9" t="s">
         <v>446</v>
       </c>
       <c r="C9" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B10" t="s">
         <v>444</v>
       </c>
       <c r="C10" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B11" t="s">
         <v>445</v>
       </c>
       <c r="C11" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B12" t="s">
         <v>449</v>
@@ -11326,7 +11335,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B13" t="s">
         <v>449</v>
@@ -11337,7 +11346,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B14" t="s">
         <v>448</v>
@@ -11348,7 +11357,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B15" t="s">
         <v>447</v>
@@ -11359,7 +11368,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B16" t="s">
         <v>448</v>
@@ -11370,7 +11379,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B17" t="s">
         <v>449</v>
@@ -11381,7 +11390,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B18" t="s">
         <v>449</v>
@@ -11392,7 +11401,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B19" t="s">
         <v>448</v>
@@ -11403,7 +11412,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B20" t="s">
         <v>447</v>
@@ -11414,7 +11423,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B21" t="s">
         <v>448</v>
@@ -11444,135 +11453,135 @@
         <v>849</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1031</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1033</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C2" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="D2" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E2" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B3" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C3" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="D3" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="E3" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B4" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="C4" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="D4" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="E4" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B5" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C5" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="D5" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="E5" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B6" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C6" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="D6" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="E6" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B7" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C7" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="D7" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="E7" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B8" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C8" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="D8" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="E8" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -11580,101 +11589,101 @@
         <v>852</v>
       </c>
       <c r="B9" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="C9" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="D9" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="E9" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B10" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="C10" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="D10" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="E10" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B11" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="C11" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="D11" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="E11" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B12" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="C12" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="D12" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="E12" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B13" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="C13" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="D13" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="E13" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B14" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="C14" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="D14" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="E14" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -11682,50 +11691,50 @@
         <v>853</v>
       </c>
       <c r="B15" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="C15" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="D15" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="E15" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B16" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="C16" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="D16" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="E16" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B17" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C17" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D17" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="E17" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -11733,50 +11742,50 @@
         <v>854</v>
       </c>
       <c r="B18" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C18" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="D18" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="E18" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B19" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C19" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="D19" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="E19" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B20" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C20" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="D20" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="E20" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -11784,67 +11793,67 @@
         <v>855</v>
       </c>
       <c r="B21" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C21" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D21" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="E21" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B22" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C22" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="D22" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="E22" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B23" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C23" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="D23" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="E23" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B24" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C24" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="D24" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="E24" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -11852,50 +11861,50 @@
         <v>856</v>
       </c>
       <c r="B25" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C25" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="D25" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="E25" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B26" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C26" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="D26" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="E26" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B27" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C27" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="D27" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="E27" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -11903,237 +11912,237 @@
         <v>857</v>
       </c>
       <c r="B28" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="C28" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="D28" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="E28" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B29" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C29" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="D29" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="E29" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B30" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C30" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="D30" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="E30" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B31" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C31" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="D31" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="E31" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B32" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C32" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="D32" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="E32" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B33" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C33" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="D33" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="E33" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B34" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C34" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="D34" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="E34" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B35" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C35" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="D35" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="E35" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B36" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="C36" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="D36" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="E36" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B37" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C37" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="D37" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="E37" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B38" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C38" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="D38" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="E38" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B39" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C39" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="D39" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="E39" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B40" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C40" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="D40" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="E40" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B41" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C41" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="D41" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="E41" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -12141,33 +12150,33 @@
         <v>858</v>
       </c>
       <c r="B42" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C42" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="D42" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="E42" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B43" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C43" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="D43" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="E43" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -12175,33 +12184,33 @@
         <v>859</v>
       </c>
       <c r="B44" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C44" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="D44" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="E44" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B45" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C45" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="D45" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="E45" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -12209,33 +12218,33 @@
         <v>860</v>
       </c>
       <c r="B46" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C46" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="D46" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="E46" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B47" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C47" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D47" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="E47" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -12243,169 +12252,169 @@
         <v>880</v>
       </c>
       <c r="B48" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C48" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="D48" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="E48" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B49" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C49" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="D49" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="E49" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B50" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C50" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="D50" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="E50" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B51" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C51" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="D51" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="E51" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B52" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C52" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="D52" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="E52" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B53" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C53" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="D53" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="E53" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B54" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C54" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="D54" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="E54" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B55" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C55" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="D55" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="E55" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B56" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C56" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="D56" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E56" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B57" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C57" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="D57" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="E57" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -12413,16 +12422,16 @@
         <v>861</v>
       </c>
       <c r="B58" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C58" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D58" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="E58" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
@@ -12430,33 +12439,33 @@
         <v>862</v>
       </c>
       <c r="B59" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C59" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="D59" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="E59" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B60" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C60" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="D60" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="E60" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
@@ -12464,220 +12473,220 @@
         <v>863</v>
       </c>
       <c r="B61" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C61" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="D61" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="E61" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B62" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="C62" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="D62" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="E62" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B63" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C63" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="D63" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="E63" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B64" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="C64" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="D64" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="E64" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B65" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C65" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="D65" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="E65" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B66" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C66" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="D66" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E66" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B67" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C67" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="D67" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="E67" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B68" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C68" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="D68" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="E68" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B69" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C69" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="D69" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="E69" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B70" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C70" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D70" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="E70" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B71" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="C71" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D71" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="E71" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B72" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="C72" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D72" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="E72" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B73" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="C73" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D73" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="E73" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
@@ -12685,135 +12694,135 @@
         <v>879</v>
       </c>
       <c r="B74" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C74" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D74" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="E74" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B75" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C75" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D75" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="E75" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B76" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C76" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D76" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="E76" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B77" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="C77" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D77" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="E77" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B78" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="C78" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="D78" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="E78" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B79" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C79" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="D79" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="E79" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B80" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C80" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="D80" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="E80" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B81" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C81" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D81" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="E81" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
@@ -12821,50 +12830,50 @@
         <v>864</v>
       </c>
       <c r="B82" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="C82" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="D82" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="E82" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B83" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="C83" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="D83" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="E83" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B84" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="C84" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="D84" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="E84" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
@@ -12872,16 +12881,16 @@
         <v>865</v>
       </c>
       <c r="B85" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="C85" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="D85" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="E85" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
@@ -12889,16 +12898,16 @@
         <v>866</v>
       </c>
       <c r="B86" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="C86" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="D86" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="E86" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
@@ -12906,101 +12915,101 @@
         <v>867</v>
       </c>
       <c r="B87" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C87" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="D87" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="E87" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B88" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C88" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="D88" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="E88" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B89" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C89" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="D89" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="E89" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B90" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C90" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="D90" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="E90" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B91" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C91" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="D91" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="E91" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B92" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C92" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="D92" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="E92" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
@@ -13008,101 +13017,101 @@
         <v>878</v>
       </c>
       <c r="B93" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="C93" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="D93" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="E93" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B94" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C94" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="D94" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="E94" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B95" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C95" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="D95" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="E95" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B96" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="C96" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="D96" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="E96" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B97" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C97" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="D97" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="E97" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B98" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C98" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="D98" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="E98" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
@@ -13110,475 +13119,475 @@
         <v>868</v>
       </c>
       <c r="B99" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C99" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="D99" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="E99" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B100" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C100" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="D100" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="E100" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B101" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C101" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="D101" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="E101" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B102" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C102" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="D102" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="E102" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B103" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C103" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="D103" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="E103" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B104" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="C104" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="D104" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="E104" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B105" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C105" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="D105" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="E105" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B106" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C106" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="D106" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="E106" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B107" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C107" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="D107" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="E107" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B108" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C108" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="D108" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="E108" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B109" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C109" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="D109" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="E109" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B110" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C110" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="D110" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="E110" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B111" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C111" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="D111" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="E111" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B112" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C112" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="D112" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="E112" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B113" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C113" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="D113" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="E113" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B114" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="C114" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="D114" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="E114" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B115" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="C115" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="D115" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="E115" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B116" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="C116" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="D116" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="E116" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B117" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="C117" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="D117" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="E117" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B118" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="C118" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="D118" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="E118" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B119" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="C119" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="D119" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="E119" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B120" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C120" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="D120" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="E120" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B121" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C121" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="D121" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="E121" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B122" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C122" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="D122" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="E122" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B123" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="C123" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="D123" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="E123" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B124" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="C124" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D124" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="E124" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B125" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="C125" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D125" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="E125" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="B126" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="C126" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="D126" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="E126" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
@@ -13586,237 +13595,237 @@
         <v>869</v>
       </c>
       <c r="B127" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C127" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D127" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="E127" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B128" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C128" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="D128" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="E128" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B129" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C129" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="D129" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="E129" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B130" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="C130" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="D130" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="E130" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B131" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="C131" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="D131" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="E131" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B132" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C132" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="D132" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="E132" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B133" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C133" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="D133" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="E133" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B134" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="C134" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="D134" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="E134" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B135" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C135" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="D135" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="E135" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B136" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C136" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="D136" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="E136" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B137" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="C137" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="D137" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="E137" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B138" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="C138" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="D138" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="E138" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B139" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="C139" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="D139" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="E139" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B140" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="C140" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="D140" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="E140" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
@@ -13824,152 +13833,152 @@
         <v>870</v>
       </c>
       <c r="B141" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="C141" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="D141" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="E141" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B142" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C142" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="D142" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="E142" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B143" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="C143" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="D143" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="E143" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B144" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="C144" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="D144" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="E144" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B145" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C145" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="D145" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="E145" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B146" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="C146" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="D146" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="E146" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B147" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="C147" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="D147" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="E147" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B148" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="C148" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="D148" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="E148" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B149" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="C149" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="D149" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="E149" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
@@ -13977,33 +13986,33 @@
         <v>871</v>
       </c>
       <c r="B150" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="C150" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="D150" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="E150" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B151" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="C151" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="D151" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="E151" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
@@ -14011,16 +14020,16 @@
         <v>872</v>
       </c>
       <c r="B152" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C152" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="D152" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="E152" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
@@ -14028,594 +14037,594 @@
         <v>873</v>
       </c>
       <c r="B153" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="C153" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="D153" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="E153" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B154" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="C154" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="D154" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="E154" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B155" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="C155" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="D155" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="E155" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B156" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="C156" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="D156" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="E156" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B157" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="C157" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="D157" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="E157" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B158" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="C158" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="D158" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="E158" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B159" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C159" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="D159" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="E159" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B160" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="C160" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="D160" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="E160" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B161" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="C161" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="D161" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="E161" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B162" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C162" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="D162" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="E162" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B163" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="C163" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="D163" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="E163" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B164" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="C164" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="D164" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="E164" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B165" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="C165" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="D165" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="E165" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B166" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="C166" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="D166" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="E166" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B167" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="C167" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="D167" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="E167" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B168" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="C168" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="D168" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="E168" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B169" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="C169" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="D169" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="E169" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B170" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="C170" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="D170" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="E170" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B171" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="C171" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="D171" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="E171" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B172" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="C172" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="D172" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="E172" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B173" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="C173" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="D173" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="E173" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B174" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="C174" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="D174" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="E174" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B175" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="C175" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="D175" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="E175" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B176" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C176" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="D176" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="E176" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B177" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="C177" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="D177" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="E177" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B178" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="C178" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="D178" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="E178" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B179" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="C179" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="D179" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="E179" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B180" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="C180" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="D180" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="E180" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B181" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C181" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="D181" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="E181" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B182" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="C182" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="D182" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="E182" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B183" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="C183" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="D183" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E183" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B184" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="C184" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="D184" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="E184" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B185" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C185" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="D185" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="E185" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B186" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="C186" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="D186" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="E186" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B187" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C187" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="D187" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="E187" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
@@ -14623,152 +14632,152 @@
         <v>874</v>
       </c>
       <c r="B188" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="C188" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="D188" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="E188" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B189" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C189" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="D189" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="E189" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B190" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C190" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="D190" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="E190" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B191" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C191" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="D191" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="E191" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B192" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="C192" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="D192" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="E192" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B193" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="C193" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="D193" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="E193" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B194" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="C194" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="D194" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="E194" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B195" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="C195" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="D195" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="E195" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B196" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="C196" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="D196" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="E196" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
@@ -14776,220 +14785,220 @@
         <v>875</v>
       </c>
       <c r="B197" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="C197" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="D197" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="E197" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B198" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="C198" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="D198" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="E198" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B199" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="C199" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="D199" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="E199" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B200" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="C200" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="D200" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="E200" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B201" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="C201" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="D201" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="E201" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B202" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="C202" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="D202" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="E202" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B203" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="C203" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="D203" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="E203" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B204" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="C204" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="D204" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="E204" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B205" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="C205" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="D205" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="E205" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="B206" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="C206" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="D206" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="E206" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B207" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="C207" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="D207" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="E207" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B208" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C208" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="D208" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="E208" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B209" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C209" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="D209" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="E209" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
@@ -14997,50 +15006,50 @@
         <v>876</v>
       </c>
       <c r="B210" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="C210" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="D210" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="E210" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B211" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="C211" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="D211" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="E211" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B212" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="C212" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="D212" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="E212" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
@@ -15048,84 +15057,84 @@
         <v>877</v>
       </c>
       <c r="B213" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="C213" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="D213" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="E213" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B214" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="C214" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="D214" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="E214" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B215" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="C215" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="D215" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="E215" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B216" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="C216" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="D216" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="E216" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="B217" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="C217" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="D217" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="E217" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
   </sheetData>
@@ -15148,7 +15157,7 @@
         <v>881</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -15460,30 +15469,30 @@
         <v>718</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1878</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1879</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1880</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1881</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="B2" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="C2" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="E2" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -15491,47 +15500,47 @@
         <v>748</v>
       </c>
       <c r="B3" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="C3" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="D3" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E3" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="B4" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="C4" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="D4" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="B5" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="C5" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="D5" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E5" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -15539,16 +15548,16 @@
         <v>749</v>
       </c>
       <c r="B6" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="C6" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="D6" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E6" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -15556,16 +15565,16 @@
         <v>757</v>
       </c>
       <c r="B7" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="C7" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D7" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E7" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -15573,50 +15582,50 @@
         <v>750</v>
       </c>
       <c r="B8" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="C8" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="D8" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E8" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="B9" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="C9" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="D9" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E9" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="B10" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="C10" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="D10" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E10" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -15624,30 +15633,30 @@
         <v>755</v>
       </c>
       <c r="B11" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="C11" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="D11" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="B12" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="C12" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="D12" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E12" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -15655,30 +15664,30 @@
         <v>753</v>
       </c>
       <c r="B13" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="C13" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="D13" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="B14" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="C14" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="D14" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E14" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -15686,47 +15695,47 @@
         <v>754</v>
       </c>
       <c r="B15" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="C15" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="D15" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E15" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="B16" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="C16" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="E16" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="B17" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="C17" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="D17" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E17" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -15734,50 +15743,50 @@
         <v>758</v>
       </c>
       <c r="B18" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="C18" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="D18" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E18" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="B19" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="C19" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="D19" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E19" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="B20" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="C20" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="D20" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E20" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -15785,33 +15794,33 @@
         <v>747</v>
       </c>
       <c r="B21" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="C21" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="D21" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E21" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="B22" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="C22" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="D22" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E22" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -15819,120 +15828,120 @@
         <v>751</v>
       </c>
       <c r="B23" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="C23" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="D23" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E23" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="B24" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="C24" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="D24" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E24" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="B25" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="C25" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="D25" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="E25" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B26" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="C26" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="D26" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="B27" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="C27" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="D27" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="B28" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="C28" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="D28" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="B29" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="C29" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="D29" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="B30" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="C30" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="D30" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -15940,112 +15949,112 @@
         <v>745</v>
       </c>
       <c r="B31" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="C31" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="D31" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="E31" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="B32" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="C32" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="D32" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="E32" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="B33" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="C33" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="D33" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="E33" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="B34" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="C34" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="D34" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="E34" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="B35" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="C35" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="D35" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="B36" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="C36" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="D36" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="E36" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="B37" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="C37" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="D37" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -16053,16 +16062,16 @@
         <v>746</v>
       </c>
       <c r="B38" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="C38" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="D38" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="E38" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -16070,64 +16079,64 @@
         <v>736</v>
       </c>
       <c r="B39" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="C39" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="D39" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="E39" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="B40" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="C40" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="D40" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B41" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="C41" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="D41" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="E41" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="B42" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="C42" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="D42" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="E42" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -16135,13 +16144,13 @@
         <v>744</v>
       </c>
       <c r="B43" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="C43" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="D43" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -16149,13 +16158,13 @@
         <v>743</v>
       </c>
       <c r="B44" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="C44" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="D44" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -16163,27 +16172,27 @@
         <v>726</v>
       </c>
       <c r="B45" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="C45" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="D45" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="B46" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="C46" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="D46" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -16191,16 +16200,16 @@
         <v>725</v>
       </c>
       <c r="B47" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="C47" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="D47" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="E47" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -16208,13 +16217,13 @@
         <v>735</v>
       </c>
       <c r="B48" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="C48" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="D48" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -16222,13 +16231,13 @@
         <v>733</v>
       </c>
       <c r="B49" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="C49" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="D49" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -16236,27 +16245,27 @@
         <v>734</v>
       </c>
       <c r="B50" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="C50" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="D50" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="B51" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="C51" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="D51" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -16264,13 +16273,13 @@
         <v>731</v>
       </c>
       <c r="B52" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="C52" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="D52" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -16278,27 +16287,27 @@
         <v>732</v>
       </c>
       <c r="B53" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="C53" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="D53" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="B54" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="C54" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="D54" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -16306,13 +16315,13 @@
         <v>727</v>
       </c>
       <c r="B55" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="C55" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="D55" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -16320,13 +16329,13 @@
         <v>729</v>
       </c>
       <c r="B56" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="C56" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="D56" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
@@ -16334,13 +16343,13 @@
         <v>730</v>
       </c>
       <c r="B57" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="C57" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="D57" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -16348,55 +16357,55 @@
         <v>728</v>
       </c>
       <c r="B58" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="C58" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="D58" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="B59" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="C59" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="D59" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B60" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="C60" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="D60" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="B61" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="C61" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="D61" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -16404,30 +16413,30 @@
         <v>737</v>
       </c>
       <c r="B62" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="C62" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="D62" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="E62" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="B63" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="C63" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="D63" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
@@ -16435,13 +16444,13 @@
         <v>740</v>
       </c>
       <c r="B64" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="C64" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="D64" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -16449,13 +16458,13 @@
         <v>739</v>
       </c>
       <c r="B65" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="C65" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="D65" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -16463,16 +16472,16 @@
         <v>742</v>
       </c>
       <c r="B66" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="C66" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="D66" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="E66" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -16480,13 +16489,13 @@
         <v>741</v>
       </c>
       <c r="B67" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="C67" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="D67" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
@@ -16494,16 +16503,16 @@
         <v>752</v>
       </c>
       <c r="B68" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="C68" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="D68" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="E68" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
@@ -16511,16 +16520,16 @@
         <v>756</v>
       </c>
       <c r="B69" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="C69" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="D69" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="E69" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
     </row>
   </sheetData>
@@ -16580,79 +16589,79 @@
         <v>443</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="9" t="s">
         <v>444</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="9">
         <v>-6.5</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="9" t="s">
         <v>584</v>
       </c>
-      <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="6" t="s">
+      <c r="E2" s="9">
+        <v>1</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="G2" s="6" t="b">
+      <c r="G2" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="9" t="s">
         <v>598</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="9" t="s">
         <v>687</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="9" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="C3" s="6">
-        <v>-102.1</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="3">
+        <v>-88</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="G3" s="6" t="b">
+      <c r="G3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="3" t="s">
         <v>690</v>
       </c>
     </row>
@@ -16664,7 +16673,7 @@
         <v>446</v>
       </c>
       <c r="C4" s="9">
-        <v>-75.099999999999994</v>
+        <v>-50</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>584</v>
@@ -16694,117 +16703,117 @@
         <v>690</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="5" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="9" t="s">
         <v>447</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="9">
         <v>-6.5</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="9" t="s">
         <v>584</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="E5" s="9">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="G5" t="b">
+      <c r="G5" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="9" t="s">
         <v>598</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="9" t="s">
         <v>687</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="9" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="C6">
-        <v>-102.1</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="12">
+        <v>-85</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="E6" s="7">
-        <v>1</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G6" s="7" t="b">
+      <c r="G6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="3" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="C7">
-        <v>-41.2</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="C7" s="11">
+        <v>-50.2</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>584</v>
       </c>
-      <c r="E7" s="6">
-        <v>1</v>
-      </c>
-      <c r="F7" s="6" t="s">
+      <c r="E7" s="11">
+        <v>1</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="G7" s="6" t="b">
+      <c r="G7" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="11" t="s">
         <v>602</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="11" t="s">
         <v>687</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="11" t="s">
         <v>690</v>
       </c>
     </row>
@@ -17574,237 +17583,237 @@
         <v>696</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="C28" s="4">
-        <f>-3.04/3</f>
-        <v>-1.0133333333333334</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="C28" s="9">
+        <f>-0.0001</f>
+        <v>-1E-4</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>589</v>
       </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="E28" s="9">
+        <v>1</v>
+      </c>
+      <c r="F28" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="G28" t="b">
+      <c r="G28" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="9" t="s">
         <v>619</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="K28" t="s">
+      <c r="K28" s="9" t="s">
         <v>688</v>
       </c>
-      <c r="L28" t="s">
+      <c r="L28" s="9" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
+    <row r="29" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="C29" s="6">
-        <f>-0.01</f>
-        <v>-0.01</v>
-      </c>
-      <c r="D29" s="6" t="s">
+      <c r="C29" s="3">
+        <f t="shared" ref="C29:C33" si="0">-0.0001</f>
+        <v>-1E-4</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="E29" s="6">
-        <v>1</v>
-      </c>
-      <c r="F29" s="6" t="s">
+      <c r="E29" s="3">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="G29" s="6" t="b">
+      <c r="G29" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H29" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="J29" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="K29" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="L29" s="6" t="s">
+      <c r="L29" s="3" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="9" t="s">
         <v>472</v>
       </c>
-      <c r="C30" s="4">
-        <f>-0.64/3</f>
-        <v>-0.21333333333333335</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="C30" s="9">
+        <f t="shared" si="0"/>
+        <v>-1E-4</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>589</v>
       </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="E30" s="9">
+        <v>1</v>
+      </c>
+      <c r="F30" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="G30" t="b">
+      <c r="G30" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="9" t="s">
         <v>621</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J30" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="K30" t="s">
+      <c r="K30" s="9" t="s">
         <v>688</v>
       </c>
-      <c r="L30" t="s">
+      <c r="L30" s="9" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="31" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
+    <row r="31" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C31" s="6">
-        <f>-0.009</f>
-        <v>-8.9999999999999993E-3</v>
-      </c>
-      <c r="D31" s="6" t="s">
+      <c r="C31" s="3">
+        <f t="shared" si="0"/>
+        <v>-1E-4</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="E31" s="6">
-        <v>1</v>
-      </c>
-      <c r="F31" s="6" t="s">
+      <c r="E31" s="3">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="G31" s="6" t="b">
+      <c r="G31" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="H31" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="J31" s="6" t="s">
+      <c r="J31" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="K31" s="6" t="s">
+      <c r="K31" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="L31" s="6" t="s">
+      <c r="L31" s="3" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="32" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
+    <row r="32" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="C32" s="6">
-        <f>-0.009</f>
-        <v>-8.9999999999999993E-3</v>
-      </c>
-      <c r="D32" s="6" t="s">
+      <c r="C32" s="3">
+        <f t="shared" si="0"/>
+        <v>-1E-4</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="E32" s="6">
-        <v>1</v>
-      </c>
-      <c r="F32" s="6" t="s">
+      <c r="E32" s="3">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G32" s="6" t="b">
+      <c r="G32" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="H32" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I32" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="J32" s="6" t="s">
+      <c r="J32" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="K32" s="6" t="s">
+      <c r="K32" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="L32" s="6" t="s">
+      <c r="L32" s="3" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="33" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="C33" s="6">
-        <f>-0.009</f>
-        <v>-8.9999999999999993E-3</v>
-      </c>
-      <c r="D33" s="6" t="s">
+      <c r="C33" s="9">
+        <f t="shared" si="0"/>
+        <v>-1E-4</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>589</v>
       </c>
-      <c r="E33" s="6">
-        <v>1</v>
-      </c>
-      <c r="F33" s="6" t="s">
+      <c r="E33" s="9">
+        <v>1</v>
+      </c>
+      <c r="F33" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="G33" s="6" t="b">
+      <c r="G33" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="H33" s="9" t="s">
         <v>623</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I33" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="J33" s="6" t="s">
+      <c r="J33" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="K33" s="6" t="s">
+      <c r="K33" s="9" t="s">
         <v>688</v>
       </c>
-      <c r="L33" s="6" t="s">
+      <c r="L33" s="9" t="s">
         <v>697</v>
       </c>
     </row>
@@ -23799,50 +23808,50 @@
         <v>824</v>
       </c>
     </row>
-    <row r="25" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="9" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="C25" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="9">
+        <v>99</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>767</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>2047</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>737</v>
-      </c>
-      <c r="C25" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="D25" s="7">
+      <c r="I25" s="9">
+        <v>5</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>797</v>
+      </c>
+      <c r="K25" s="9">
+        <v>1</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="M25" s="9">
         <v>99</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>767</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>2048</v>
-      </c>
-      <c r="I25" s="7">
-        <v>-10</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>797</v>
-      </c>
-      <c r="K25" s="7">
-        <v>1</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="M25" s="7">
-        <v>99</v>
-      </c>
-      <c r="N25" s="7" t="b">
+      <c r="N25" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="O25" s="7" t="s">
+      <c r="O25" s="9" t="s">
         <v>825</v>
       </c>
     </row>
@@ -23975,7 +23984,7 @@
         <v>1</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="M28" s="7">
         <v>1</v>
@@ -24299,7 +24308,7 @@
         <v>500000000</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="K35" s="3">
         <v>0.96</v>
@@ -24792,7 +24801,7 @@
         <v>207</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="C46" s="6" t="b">
         <v>1</v>
@@ -24834,50 +24843,50 @@
         <v>838</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+    <row r="47" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="9" t="s">
         <v>756</v>
       </c>
-      <c r="C47" t="b">
-        <v>1</v>
-      </c>
-      <c r="D47">
+      <c r="C47" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D47" s="9">
         <v>99</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G47" s="9" t="s">
         <v>775</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H47" s="9" t="s">
         <v>505</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="9">
         <v>0</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J47" s="9" t="s">
         <v>593</v>
       </c>
-      <c r="K47">
+      <c r="K47" s="9">
         <v>0</v>
       </c>
-      <c r="L47" t="s">
+      <c r="L47" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="M47">
+      <c r="M47" s="9">
         <v>99</v>
       </c>
-      <c r="N47" t="b">
+      <c r="N47" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="O47" t="s">
+      <c r="O47" s="9" t="s">
         <v>839</v>
       </c>
     </row>
@@ -24975,153 +24984,153 @@
         <v>841</v>
       </c>
     </row>
-    <row r="50" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
+    <row r="50" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="9" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="C50" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D50" s="9">
+        <v>99</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>2041</v>
+      </c>
+      <c r="I50" s="9">
+        <v>-10</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>804</v>
+      </c>
+      <c r="K50" s="9">
+        <v>1</v>
+      </c>
+      <c r="L50" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="M50" s="9">
+        <v>99</v>
+      </c>
+      <c r="N50" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O50" s="9" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="9" t="s">
         <v>2039</v>
       </c>
-      <c r="B50" s="6" t="s">
-        <v>758</v>
-      </c>
-      <c r="C50" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D50" s="6">
+      <c r="B51" s="9" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C51" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D51" s="9">
         <v>99</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E51" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F51" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="G50" s="6" t="s">
+      <c r="G51" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="H50" s="6" t="s">
+      <c r="H51" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="I51" s="9">
+        <v>-0.2</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>804</v>
+      </c>
+      <c r="K51" s="9">
+        <v>1</v>
+      </c>
+      <c r="L51" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="M51" s="9">
+        <v>99</v>
+      </c>
+      <c r="N51" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O51" s="9" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="9" t="s">
+        <v>2040</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C52" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D52" s="9">
+        <v>99</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="H52" s="9" t="s">
         <v>2042</v>
       </c>
-      <c r="I50" s="6">
-        <v>10</v>
-      </c>
-      <c r="J50" s="6" t="s">
+      <c r="I52" s="9">
+        <v>-0.3</v>
+      </c>
+      <c r="J52" s="9" t="s">
         <v>804</v>
       </c>
-      <c r="K50" s="6">
-        <v>1</v>
-      </c>
-      <c r="L50" s="6" t="s">
+      <c r="K52" s="9">
+        <v>1</v>
+      </c>
+      <c r="L52" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="M50" s="6">
+      <c r="M52" s="9">
         <v>99</v>
       </c>
-      <c r="N50" s="6" t="b">
+      <c r="N52" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="O50" s="6" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="6" t="s">
-        <v>2040</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>1892</v>
-      </c>
-      <c r="C51" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D51" s="6">
-        <v>99</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>776</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="I51" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>804</v>
-      </c>
-      <c r="K51" s="6">
-        <v>1</v>
-      </c>
-      <c r="L51" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="M51" s="6">
-        <v>99</v>
-      </c>
-      <c r="N51" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O51" s="6" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="6" t="s">
-        <v>2041</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>1891</v>
-      </c>
-      <c r="C52" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D52" s="6">
-        <v>99</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>776</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>2043</v>
-      </c>
-      <c r="I52" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="J52" s="6" t="s">
-        <v>804</v>
-      </c>
-      <c r="K52" s="6">
-        <v>1</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="M52" s="6">
-        <v>99</v>
-      </c>
-      <c r="N52" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O52" s="6" t="s">
+      <c r="O52" s="9" t="s">
         <v>842</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="C53" s="6" t="b">
         <v>1</v>
@@ -25139,13 +25148,13 @@
         <v>763</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="I53" s="6">
         <v>20000000</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="K53" s="6">
         <v>1</v>
@@ -25160,15 +25169,15 @@
         <v>0</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="C54" s="6" t="b">
         <v>1</v>
@@ -25186,13 +25195,13 @@
         <v>763</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="I54" s="6">
         <v>7500000</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="K54" s="6">
         <v>1</v>
@@ -25207,7 +25216,7 @@
         <v>0</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
     </row>
   </sheetData>
@@ -26376,35 +26385,35 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="B2">
-        <v>-40</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="10">
+        <v>-140</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>593</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" s="10">
+        <v>1</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>886</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="10" t="s">
         <v>890</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="10">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>894</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="H2" s="10" t="s">
+        <v>895</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>431</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="10" t="s">
         <v>351</v>
       </c>
     </row>
@@ -26431,7 +26440,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="I3" t="s">
         <v>431</v>
@@ -26440,35 +26449,35 @@
         <v>351</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
         <v>512</v>
       </c>
-      <c r="B4">
-        <v>-50</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="10">
+        <v>-140</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>593</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" s="10">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>888</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="10" t="s">
         <v>892</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="10">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
-        <v>896</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="H4" s="10" t="s">
+        <v>2059</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>431</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="10" t="s">
         <v>351</v>
       </c>
     </row>
@@ -26495,7 +26504,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="I5" t="s">
         <v>431</v>
@@ -26523,27 +26532,27 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>899</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="D2" t="s">
         <v>351</v>
@@ -26551,13 +26560,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B3" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="D3" t="s">
         <v>351</v>
@@ -26565,13 +26574,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B4" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C4" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D4" t="s">
         <v>351</v>
@@ -26579,436 +26588,436 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B5" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C5" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D5" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B6" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C6" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="D6" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B7" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C7" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D7" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B8" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C8" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="D8" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B9" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C9" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D9" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B10" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C10" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="D10" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B11" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C11" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D11" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B12" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C12" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D12" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B13" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C13" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="D13" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B14" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="C14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="D14" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B15" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C15" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="D15" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B16" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C16" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="D16" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B17" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C17" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D17" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B18" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C18" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="D18" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B19" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C19" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D19" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B20" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C20" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="D20" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B21" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C21" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="D21" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B22" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C22" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="D22" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B23" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C23" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D23" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B24" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C24" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D24" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B25" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C25" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D25" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B26" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C26" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D26" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B27" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C27" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="D27" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B28" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C28" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D28" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B29" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C29" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D29" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B30" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C30" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D30" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B31" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C31" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="D31" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B32" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C32" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D32" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B33" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C33" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D33" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B34" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C34" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D34" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B35" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="C35" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D35" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
   </sheetData>

--- a/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
+++ b/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tony/Documents/sisepuede_modeling/ssp_bulgaria/ssp_modeling/cost-benefits/cb_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC5D005-B545-884F-BA1C-4014CF80871F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35302E24-9C83-754B-8BD7-910CA3A1A3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="660" windowWidth="27500" windowHeight="17660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5320" yWindow="5220" windowWidth="27500" windowHeight="17660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -6296,7 +6296,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6351,6 +6351,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -6383,7 +6389,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -6397,8 +6403,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -16748,7 +16753,7 @@
       <c r="B6" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="3">
         <v>-85</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -16779,41 +16784,41 @@
         <v>690</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" t="s">
         <v>449</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7">
         <v>-50.2</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" t="s">
         <v>584</v>
       </c>
-      <c r="E7" s="11">
-        <v>1</v>
-      </c>
-      <c r="F7" s="11" t="s">
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
         <v>216</v>
       </c>
-      <c r="G7" s="11" t="b">
+      <c r="G7" t="b">
         <v>0</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" t="s">
         <v>602</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" t="s">
         <v>378</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" t="s">
         <v>350</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" t="s">
         <v>687</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" t="s">
         <v>690</v>
       </c>
     </row>
@@ -17121,79 +17126,79 @@
         <v>693</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+    <row r="16" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="11" t="s">
         <v>458</v>
       </c>
-      <c r="C16">
-        <v>500</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C16" s="11">
+        <v>1000</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="E16" s="11">
+        <v>1</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="G16" t="b">
+      <c r="G16" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="11" t="s">
         <v>607</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L16" t="s">
+      <c r="L16" s="11" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+    <row r="17" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="C17">
-        <v>200</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="E17" s="3">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="G17" t="b">
+      <c r="G17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="L17" t="s">
+      <c r="L17" s="3" t="s">
         <v>694</v>
       </c>
     </row>
@@ -18197,497 +18202,497 @@
         <v>699</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+    <row r="44" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="11" t="s">
         <v>486</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="11">
         <v>600</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="E44">
-        <v>1</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="E44" s="11">
+        <v>1</v>
+      </c>
+      <c r="F44" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="G44" t="b">
+      <c r="G44" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H44" s="11" t="s">
         <v>630</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="11" t="s">
         <v>679</v>
       </c>
-      <c r="J44" t="s">
+      <c r="J44" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="K44" t="s">
+      <c r="K44" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L44" t="s">
+      <c r="L44" s="11" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+    <row r="45" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="11">
+        <v>170</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>591</v>
+      </c>
+      <c r="E45" s="11">
+        <v>1</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="G45" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>679</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>688</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="C46" s="11">
         <v>285</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D46" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="E45">
-        <v>1</v>
-      </c>
-      <c r="F45" t="s">
-        <v>254</v>
-      </c>
-      <c r="G45" t="b">
+      <c r="E46" s="11">
+        <v>1</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="G46" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H45" t="s">
-        <v>631</v>
-      </c>
-      <c r="I45" t="s">
+      <c r="H46" s="11" t="s">
+        <v>632</v>
+      </c>
+      <c r="I46" s="11" t="s">
         <v>679</v>
       </c>
-      <c r="J45" t="s">
+      <c r="J46" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="K45" t="s">
+      <c r="K46" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L45" t="s">
+      <c r="L46" s="11" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>49</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="C46" s="3">
-        <v>285</v>
-      </c>
-      <c r="D46" t="s">
+    <row r="47" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>489</v>
+      </c>
+      <c r="C47" s="11">
+        <v>300</v>
+      </c>
+      <c r="D47" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="E46">
-        <v>1</v>
-      </c>
-      <c r="F46" t="s">
-        <v>255</v>
-      </c>
-      <c r="G46" t="b">
+      <c r="E47" s="11">
+        <v>1</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="G47" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H46" t="s">
-        <v>632</v>
-      </c>
-      <c r="I46" t="s">
+      <c r="H47" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="I47" s="11" t="s">
         <v>679</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J47" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="K46" t="s">
+      <c r="K47" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L46" t="s">
+      <c r="L47" s="11" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>50</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="C47" s="3">
+    <row r="48" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="C48" s="11">
         <v>300</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D48" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="E47">
-        <v>1</v>
-      </c>
-      <c r="F47" t="s">
-        <v>256</v>
-      </c>
-      <c r="G47" t="b">
+      <c r="E48" s="11">
+        <v>1</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="G48" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H47" t="s">
-        <v>633</v>
-      </c>
-      <c r="I47" t="s">
+      <c r="H48" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="I48" s="11" t="s">
         <v>679</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J48" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="K47" t="s">
+      <c r="K48" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L47" t="s">
+      <c r="L48" s="11" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>51</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="C48" s="3">
+    <row r="49" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="C49" s="11">
+        <v>500</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>591</v>
+      </c>
+      <c r="E49" s="11">
+        <v>1</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="G49" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>634</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>679</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>688</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="C50" s="11">
         <v>300</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D50" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="E48">
-        <v>1</v>
-      </c>
-      <c r="F48" t="s">
-        <v>257</v>
-      </c>
-      <c r="G48" t="b">
+      <c r="E50" s="11">
+        <v>1</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="G50" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H50" s="11" t="s">
         <v>630</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I50" s="11" t="s">
         <v>679</v>
       </c>
-      <c r="J48" t="s">
+      <c r="J50" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="K48" t="s">
+      <c r="K50" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L48" t="s">
+      <c r="L50" s="11" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="C49" s="3">
+    <row r="51" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="C51" s="11">
+        <v>400</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>591</v>
+      </c>
+      <c r="E51" s="11">
+        <v>1</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="G51" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>679</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>688</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="C52" s="11">
         <v>500</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D52" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="E49">
-        <v>1</v>
-      </c>
-      <c r="F49" t="s">
-        <v>258</v>
-      </c>
-      <c r="G49" t="b">
+      <c r="E52" s="11">
+        <v>1</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="G52" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H49" t="s">
-        <v>634</v>
-      </c>
-      <c r="I49" t="s">
+      <c r="H52" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="I52" s="11" t="s">
         <v>679</v>
       </c>
-      <c r="J49" t="s">
+      <c r="J52" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="K49" t="s">
+      <c r="K52" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L49" t="s">
+      <c r="L52" s="11" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>53</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="C50" s="3">
+    <row r="53" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>495</v>
+      </c>
+      <c r="C53" s="11">
         <v>300</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D53" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="E50">
-        <v>1</v>
-      </c>
-      <c r="F50" t="s">
-        <v>259</v>
-      </c>
-      <c r="G50" t="b">
+      <c r="E53" s="11">
+        <v>1</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="G53" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H50" t="s">
-        <v>630</v>
-      </c>
-      <c r="I50" t="s">
+      <c r="H53" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="I53" s="11" t="s">
         <v>679</v>
       </c>
-      <c r="J50" t="s">
+      <c r="J53" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="K50" t="s">
+      <c r="K53" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L50" t="s">
+      <c r="L53" s="11" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="C51" s="3">
-        <v>400</v>
-      </c>
-      <c r="D51" t="s">
+    <row r="54" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="C54" s="11">
+        <v>30</v>
+      </c>
+      <c r="D54" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="E51">
-        <v>1</v>
-      </c>
-      <c r="F51" t="s">
-        <v>260</v>
-      </c>
-      <c r="G51" t="b">
+      <c r="E54" s="11">
+        <v>1</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="G54" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H51" t="s">
-        <v>630</v>
-      </c>
-      <c r="I51" t="s">
+      <c r="H54" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="I54" s="11" t="s">
         <v>679</v>
       </c>
-      <c r="J51" t="s">
+      <c r="J54" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="K51" t="s">
+      <c r="K54" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L51" t="s">
+      <c r="L54" s="11" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="C52" s="3">
-        <v>500</v>
-      </c>
-      <c r="D52" t="s">
+    <row r="55" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="C55" s="11">
+        <v>300</v>
+      </c>
+      <c r="D55" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="E52">
-        <v>1</v>
-      </c>
-      <c r="F52" t="s">
-        <v>261</v>
-      </c>
-      <c r="G52" t="b">
+      <c r="E55" s="11">
+        <v>1</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="G55" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H52" t="s">
-        <v>635</v>
-      </c>
-      <c r="I52" t="s">
+      <c r="H55" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="I55" s="11" t="s">
         <v>679</v>
       </c>
-      <c r="J52" t="s">
+      <c r="J55" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="K52" t="s">
+      <c r="K55" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L52" t="s">
+      <c r="L55" s="11" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="C53" s="3">
+    <row r="56" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="C56" s="11">
         <v>300</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D56" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="E53">
-        <v>1</v>
-      </c>
-      <c r="F53" t="s">
-        <v>262</v>
-      </c>
-      <c r="G53" t="b">
+      <c r="E56" s="11">
+        <v>1</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="G56" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H53" t="s">
-        <v>636</v>
-      </c>
-      <c r="I53" t="s">
+      <c r="H56" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="I56" s="11" t="s">
         <v>679</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J56" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="K53" t="s">
+      <c r="K56" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L53" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>57</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="C54" s="3">
-        <v>30</v>
-      </c>
-      <c r="D54" t="s">
-        <v>591</v>
-      </c>
-      <c r="E54">
-        <v>1</v>
-      </c>
-      <c r="F54" t="s">
-        <v>263</v>
-      </c>
-      <c r="G54" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" t="s">
-        <v>637</v>
-      </c>
-      <c r="I54" t="s">
-        <v>679</v>
-      </c>
-      <c r="J54" t="s">
-        <v>353</v>
-      </c>
-      <c r="K54" t="s">
-        <v>688</v>
-      </c>
-      <c r="L54" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>58</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="C55" s="3">
-        <v>300</v>
-      </c>
-      <c r="D55" t="s">
-        <v>591</v>
-      </c>
-      <c r="E55">
-        <v>1</v>
-      </c>
-      <c r="F55" t="s">
-        <v>264</v>
-      </c>
-      <c r="G55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55" t="s">
-        <v>638</v>
-      </c>
-      <c r="I55" t="s">
-        <v>679</v>
-      </c>
-      <c r="J55" t="s">
-        <v>353</v>
-      </c>
-      <c r="K55" t="s">
-        <v>688</v>
-      </c>
-      <c r="L55" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>59</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="C56" s="3">
-        <v>300</v>
-      </c>
-      <c r="D56" t="s">
-        <v>591</v>
-      </c>
-      <c r="E56">
-        <v>1</v>
-      </c>
-      <c r="F56" t="s">
-        <v>265</v>
-      </c>
-      <c r="G56" t="b">
-        <v>0</v>
-      </c>
-      <c r="H56" t="s">
-        <v>639</v>
-      </c>
-      <c r="I56" t="s">
-        <v>679</v>
-      </c>
-      <c r="J56" t="s">
-        <v>353</v>
-      </c>
-      <c r="K56" t="s">
-        <v>688</v>
-      </c>
-      <c r="L56" t="s">
+      <c r="L56" s="11" t="s">
         <v>699</v>
       </c>
     </row>

--- a/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
+++ b/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tony/Documents/sisepuede_modeling/ssp_bulgaria/ssp_modeling/cost-benefits/cb_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35302E24-9C83-754B-8BD7-910CA3A1A3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E9351C-F3B4-3749-803C-68AFD0313160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5320" yWindow="5220" windowWidth="27500" windowHeight="17660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29100" yWindow="7000" windowWidth="27720" windowHeight="17980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -6296,7 +6296,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6312,12 +6312,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6357,6 +6351,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -6389,7 +6395,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -6399,11 +6405,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9830,20 +9838,20 @@
         <v>435</v>
       </c>
     </row>
-    <row r="184" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="7" t="s">
+    <row r="184" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="6" t="s">
         <v>2046</v>
       </c>
-      <c r="B184" s="7" t="s">
+      <c r="B184" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="C184" s="7" t="s">
+      <c r="C184" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="D184" s="7" t="s">
+      <c r="D184" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="E184" s="7" t="s">
+      <c r="E184" s="6" t="s">
         <v>435</v>
       </c>
     </row>
@@ -10255,82 +10263,82 @@
         <v>435</v>
       </c>
     </row>
-    <row r="209" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="7" t="s">
+    <row r="209" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A209" s="6" t="s">
         <v>2038</v>
       </c>
-      <c r="B209" s="7" t="s">
+      <c r="B209" s="6" t="s">
         <v>2043</v>
       </c>
-      <c r="C209" s="7" t="s">
+      <c r="C209" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="D209" s="7" t="s">
+      <c r="D209" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="E209" s="7" t="s">
+      <c r="E209" s="6" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="210" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="7" t="s">
+    <row r="210" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="6" t="s">
         <v>2039</v>
       </c>
-      <c r="B210" s="7" t="s">
+      <c r="B210" s="6" t="s">
         <v>2044</v>
       </c>
-      <c r="C210" s="7" t="s">
+      <c r="C210" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="D210" s="7" t="s">
+      <c r="D210" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="E210" s="7" t="s">
+      <c r="E210" s="6" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="211" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="7" t="s">
+    <row r="211" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="6" t="s">
         <v>2040</v>
       </c>
-      <c r="B211" s="7" t="s">
+      <c r="B211" s="6" t="s">
         <v>2045</v>
       </c>
-      <c r="C211" s="7" t="s">
+      <c r="C211" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="D211" s="7" t="s">
+      <c r="D211" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="E211" s="7" t="s">
+      <c r="E211" s="6" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A212" s="8" t="s">
+      <c r="A212" s="7" t="s">
         <v>2049</v>
       </c>
-      <c r="B212" s="7" t="s">
+      <c r="B212" s="6" t="s">
         <v>2054</v>
       </c>
-      <c r="C212" s="7" t="s">
+      <c r="C212" s="6" t="s">
         <v>2056</v>
       </c>
-      <c r="E212" s="7" t="s">
+      <c r="E212" s="6" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A213" s="8" t="s">
+      <c r="A213" s="7" t="s">
         <v>2050</v>
       </c>
-      <c r="B213" s="7" t="s">
+      <c r="B213" s="6" t="s">
         <v>2055</v>
       </c>
-      <c r="C213" s="7" t="s">
+      <c r="C213" s="6" t="s">
         <v>2056</v>
       </c>
-      <c r="E213" s="7" t="s">
+      <c r="E213" s="6" t="s">
         <v>435</v>
       </c>
     </row>
@@ -16594,193 +16602,193 @@
         <v>443</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="8">
         <v>-6.5</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>584</v>
       </c>
-      <c r="E2" s="9">
-        <v>1</v>
-      </c>
-      <c r="F2" s="9" t="s">
+      <c r="E2" s="8">
+        <v>1</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="G2" s="9" t="b">
+      <c r="G2" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="8" t="s">
         <v>687</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="8" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="C3" s="3">
-        <v>-88</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="11">
+        <v>-200</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>584</v>
       </c>
-      <c r="E3" s="3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="E3" s="11">
+        <v>1</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="G3" s="3" t="b">
+      <c r="G3" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="11" t="s">
         <v>599</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="11" t="s">
         <v>687</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="11" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="11" t="s">
         <v>446</v>
       </c>
-      <c r="C4" s="9">
-        <v>-50</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="11">
+        <v>-180</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>584</v>
       </c>
-      <c r="E4" s="9">
-        <v>1</v>
-      </c>
-      <c r="F4" s="9" t="s">
+      <c r="E4" s="11">
+        <v>1</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="G4" s="9" t="b">
+      <c r="G4" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="11" t="s">
         <v>600</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="11" t="s">
         <v>687</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="11" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>-6.5</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>584</v>
       </c>
-      <c r="E5" s="9">
-        <v>1</v>
-      </c>
-      <c r="F5" s="9" t="s">
+      <c r="E5" s="8">
+        <v>1</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="G5" s="9" t="b">
+      <c r="G5" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="8" t="s">
         <v>687</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="8" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="C6" s="3">
-        <v>-85</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="12">
+        <v>-90</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>584</v>
       </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="E6" s="12">
+        <v>1</v>
+      </c>
+      <c r="F6" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="G6" s="3" t="b">
+      <c r="G6" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="12" t="s">
         <v>601</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="12" t="s">
         <v>687</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="L6" s="12" t="s">
         <v>690</v>
       </c>
     </row>
@@ -17126,41 +17134,41 @@
         <v>693</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
+    <row r="16" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <v>1000</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="10" t="s">
         <v>586</v>
       </c>
-      <c r="E16" s="11">
-        <v>1</v>
-      </c>
-      <c r="F16" s="11" t="s">
+      <c r="E16" s="10">
+        <v>1</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="G16" s="11" t="b">
+      <c r="G16" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="10" t="s">
         <v>607</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="J16" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="K16" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="L16" s="10" t="s">
         <v>694</v>
       </c>
     </row>
@@ -17354,159 +17362,159 @@
         <v>695</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="6">
         <f>-18</f>
         <v>-18</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="6" t="s">
         <v>588</v>
       </c>
-      <c r="E22" s="7">
-        <v>1</v>
-      </c>
-      <c r="F22" s="7" t="s">
+      <c r="E22" s="6">
+        <v>1</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="G22" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" s="7" t="s">
+      <c r="G22" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="6" t="s">
         <v>678</v>
       </c>
-      <c r="J22" s="7" t="s">
+      <c r="J22" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="K22" s="7" t="s">
+      <c r="K22" s="6" t="s">
         <v>688</v>
       </c>
-      <c r="L22" s="7" t="s">
+      <c r="L22" s="6" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
+    <row r="23" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="5">
         <f>-18</f>
         <v>-18</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="E23" s="6">
-        <v>1</v>
-      </c>
-      <c r="F23" s="6" t="s">
+      <c r="E23" s="5">
+        <v>1</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="G23" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="6" t="s">
+      <c r="G23" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="5" t="s">
         <v>678</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="J23" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="K23" s="6" t="s">
+      <c r="K23" s="5" t="s">
         <v>688</v>
       </c>
-      <c r="L23" s="6" t="s">
+      <c r="L23" s="5" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="C24" s="4">
-        <f>-70/3</f>
-        <v>-23.333333333333332</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C24" s="11">
+        <f>-70/2</f>
+        <v>-35</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="E24" s="11">
+        <v>1</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="G24" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="G24" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" s="11" t="s">
         <v>615</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="11" t="s">
         <v>678</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L24" t="s">
+      <c r="L24" s="11" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="25" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
+    <row r="25" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="11" t="s">
         <v>467</v>
       </c>
-      <c r="C25" s="6">
-        <f>-3.2</f>
-        <v>-3.2</v>
-      </c>
-      <c r="D25" s="6" t="s">
+      <c r="C25" s="11">
+        <f>-8</f>
+        <v>-8</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="E25" s="6">
-        <v>1</v>
-      </c>
-      <c r="F25" s="6" t="s">
+      <c r="E25" s="11">
+        <v>1</v>
+      </c>
+      <c r="F25" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="G25" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25" s="6" t="s">
+      <c r="G25" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="11" t="s">
         <v>678</v>
       </c>
-      <c r="J25" s="6" t="s">
+      <c r="J25" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L25" s="6" t="s">
+      <c r="L25" s="11" t="s">
         <v>696</v>
       </c>
     </row>
@@ -17549,276 +17557,276 @@
         <v>696</v>
       </c>
     </row>
-    <row r="27" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
+    <row r="27" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="C27" s="6">
-        <f>-13</f>
-        <v>-13</v>
-      </c>
-      <c r="D27" s="6" t="s">
+      <c r="C27" s="11">
+        <f>-15</f>
+        <v>-15</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="E27" s="6">
-        <v>1</v>
-      </c>
-      <c r="F27" s="6" t="s">
+      <c r="E27" s="11">
+        <v>1</v>
+      </c>
+      <c r="F27" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="G27" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="6" t="s">
+      <c r="G27" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="11" t="s">
         <v>618</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="11" t="s">
         <v>678</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="J27" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="K27" s="6" t="s">
+      <c r="K27" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L27" s="6" t="s">
+      <c r="L27" s="11" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="28" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="9" t="s">
+    <row r="28" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="C28" s="9">
-        <f>-0.0001</f>
-        <v>-1E-4</v>
-      </c>
-      <c r="D28" s="9" t="s">
+      <c r="C28" s="11">
+        <f>-0.2</f>
+        <v>-0.2</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="E28" s="9">
-        <v>1</v>
-      </c>
-      <c r="F28" s="9" t="s">
+      <c r="E28" s="11">
+        <v>1</v>
+      </c>
+      <c r="F28" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="G28" s="9" t="b">
+      <c r="G28" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="11" t="s">
         <v>619</v>
       </c>
-      <c r="I28" s="9" t="s">
+      <c r="I28" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="J28" s="9" t="s">
+      <c r="J28" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="K28" s="9" t="s">
+      <c r="K28" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L28" s="9" t="s">
+      <c r="L28" s="11" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
+    <row r="29" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="C29" s="3">
-        <f t="shared" ref="C29:C33" si="0">-0.0001</f>
-        <v>-1E-4</v>
-      </c>
-      <c r="D29" s="3" t="s">
+      <c r="C29" s="11">
+        <f t="shared" ref="C29:C33" si="0">-0.2</f>
+        <v>-0.2</v>
+      </c>
+      <c r="D29" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="E29" s="3">
-        <v>1</v>
-      </c>
-      <c r="F29" s="3" t="s">
+      <c r="E29" s="11">
+        <v>1</v>
+      </c>
+      <c r="F29" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="G29" s="3" t="b">
+      <c r="G29" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H29" s="11" t="s">
         <v>620</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="I29" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="J29" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="K29" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="L29" s="11" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="30" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="9" t="s">
+    <row r="30" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="11">
         <f t="shared" si="0"/>
-        <v>-1E-4</v>
-      </c>
-      <c r="D30" s="9" t="s">
+        <v>-0.2</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="E30" s="9">
-        <v>1</v>
-      </c>
-      <c r="F30" s="9" t="s">
+      <c r="E30" s="11">
+        <v>1</v>
+      </c>
+      <c r="F30" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="G30" s="9" t="b">
+      <c r="G30" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="11" t="s">
         <v>621</v>
       </c>
-      <c r="I30" s="9" t="s">
+      <c r="I30" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="J30" s="9" t="s">
+      <c r="J30" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="K30" s="9" t="s">
+      <c r="K30" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L30" s="9" t="s">
+      <c r="L30" s="11" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="31" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
+    <row r="31" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="11">
         <f t="shared" si="0"/>
-        <v>-1E-4</v>
-      </c>
-      <c r="D31" s="3" t="s">
+        <v>-0.2</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="E31" s="3">
-        <v>1</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="E31" s="11">
+        <v>1</v>
+      </c>
+      <c r="F31" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="G31" s="3" t="b">
+      <c r="G31" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H31" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="I31" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="J31" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="K31" s="3" t="s">
+      <c r="K31" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L31" s="3" t="s">
+      <c r="L31" s="11" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="32" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
+    <row r="32" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="11">
         <f t="shared" si="0"/>
-        <v>-1E-4</v>
-      </c>
-      <c r="D32" s="3" t="s">
+        <v>-0.2</v>
+      </c>
+      <c r="D32" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="E32" s="3">
-        <v>1</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="E32" s="11">
+        <v>1</v>
+      </c>
+      <c r="F32" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="G32" s="3" t="b">
+      <c r="G32" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="H32" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="I32" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="J32" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="K32" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L32" s="3" t="s">
+      <c r="L32" s="11" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="33" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="9" t="s">
+    <row r="33" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="11">
         <f t="shared" si="0"/>
-        <v>-1E-4</v>
-      </c>
-      <c r="D33" s="9" t="s">
+        <v>-0.2</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="E33" s="9">
-        <v>1</v>
-      </c>
-      <c r="F33" s="9" t="s">
+      <c r="E33" s="11">
+        <v>1</v>
+      </c>
+      <c r="F33" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="G33" s="9" t="b">
+      <c r="G33" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="11" t="s">
         <v>623</v>
       </c>
-      <c r="I33" s="9" t="s">
+      <c r="I33" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="J33" s="9" t="s">
+      <c r="J33" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="K33" s="9" t="s">
+      <c r="K33" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L33" s="9" t="s">
+      <c r="L33" s="11" t="s">
         <v>697</v>
       </c>
     </row>
@@ -18202,497 +18210,497 @@
         <v>699</v>
       </c>
     </row>
-    <row r="44" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="11" t="s">
+    <row r="44" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="10" t="s">
         <v>486</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="10">
         <v>600</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D44" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="E44" s="11">
-        <v>1</v>
-      </c>
-      <c r="F44" s="11" t="s">
+      <c r="E44" s="10">
+        <v>1</v>
+      </c>
+      <c r="F44" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="G44" s="11" t="b">
+      <c r="G44" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H44" s="11" t="s">
+      <c r="H44" s="10" t="s">
         <v>630</v>
       </c>
-      <c r="I44" s="11" t="s">
+      <c r="I44" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="J44" s="11" t="s">
+      <c r="J44" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="K44" s="11" t="s">
+      <c r="K44" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="L44" s="11" t="s">
+      <c r="L44" s="10" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="45" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="11" t="s">
+    <row r="45" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="10" t="s">
         <v>487</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="10">
         <v>170</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="E45" s="11">
-        <v>1</v>
-      </c>
-      <c r="F45" s="11" t="s">
+      <c r="E45" s="10">
+        <v>1</v>
+      </c>
+      <c r="F45" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="G45" s="11" t="b">
+      <c r="G45" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H45" s="11" t="s">
+      <c r="H45" s="10" t="s">
         <v>631</v>
       </c>
-      <c r="I45" s="11" t="s">
+      <c r="I45" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="J45" s="11" t="s">
+      <c r="J45" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="K45" s="11" t="s">
+      <c r="K45" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="L45" s="11" t="s">
+      <c r="L45" s="10" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="46" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="11" t="s">
+    <row r="46" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="10" t="s">
         <v>488</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="10">
         <v>285</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="E46" s="11">
-        <v>1</v>
-      </c>
-      <c r="F46" s="11" t="s">
+      <c r="E46" s="10">
+        <v>1</v>
+      </c>
+      <c r="F46" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="G46" s="11" t="b">
+      <c r="G46" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="H46" s="10" t="s">
         <v>632</v>
       </c>
-      <c r="I46" s="11" t="s">
+      <c r="I46" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="J46" s="11" t="s">
+      <c r="J46" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="K46" s="11" t="s">
+      <c r="K46" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="L46" s="11" t="s">
+      <c r="L46" s="10" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="47" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="11" t="s">
+    <row r="47" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="10" t="s">
         <v>489</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="10">
         <v>300</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="E47" s="11">
-        <v>1</v>
-      </c>
-      <c r="F47" s="11" t="s">
+      <c r="E47" s="10">
+        <v>1</v>
+      </c>
+      <c r="F47" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="G47" s="11" t="b">
+      <c r="G47" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H47" s="11" t="s">
+      <c r="H47" s="10" t="s">
         <v>633</v>
       </c>
-      <c r="I47" s="11" t="s">
+      <c r="I47" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="J47" s="11" t="s">
+      <c r="J47" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="K47" s="11" t="s">
+      <c r="K47" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="L47" s="11" t="s">
+      <c r="L47" s="10" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="48" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="11" t="s">
+    <row r="48" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="10">
         <v>300</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="E48" s="11">
-        <v>1</v>
-      </c>
-      <c r="F48" s="11" t="s">
+      <c r="E48" s="10">
+        <v>1</v>
+      </c>
+      <c r="F48" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="G48" s="11" t="b">
+      <c r="G48" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H48" s="11" t="s">
+      <c r="H48" s="10" t="s">
         <v>630</v>
       </c>
-      <c r="I48" s="11" t="s">
+      <c r="I48" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="J48" s="11" t="s">
+      <c r="J48" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="K48" s="11" t="s">
+      <c r="K48" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="L48" s="11" t="s">
+      <c r="L48" s="10" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="49" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="11" t="s">
+    <row r="49" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="10" t="s">
         <v>491</v>
       </c>
-      <c r="C49" s="11">
+      <c r="C49" s="10">
         <v>500</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="E49" s="11">
-        <v>1</v>
-      </c>
-      <c r="F49" s="11" t="s">
+      <c r="E49" s="10">
+        <v>1</v>
+      </c>
+      <c r="F49" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="G49" s="11" t="b">
+      <c r="G49" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H49" s="11" t="s">
+      <c r="H49" s="10" t="s">
         <v>634</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="I49" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="J49" s="11" t="s">
+      <c r="J49" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="K49" s="11" t="s">
+      <c r="K49" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="L49" s="11" t="s">
+      <c r="L49" s="10" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="50" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="11" t="s">
+    <row r="50" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="10" t="s">
         <v>492</v>
       </c>
-      <c r="C50" s="11">
+      <c r="C50" s="10">
         <v>300</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D50" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="E50" s="11">
-        <v>1</v>
-      </c>
-      <c r="F50" s="11" t="s">
+      <c r="E50" s="10">
+        <v>1</v>
+      </c>
+      <c r="F50" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="G50" s="11" t="b">
+      <c r="G50" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H50" s="11" t="s">
+      <c r="H50" s="10" t="s">
         <v>630</v>
       </c>
-      <c r="I50" s="11" t="s">
+      <c r="I50" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="J50" s="11" t="s">
+      <c r="J50" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="K50" s="11" t="s">
+      <c r="K50" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="L50" s="11" t="s">
+      <c r="L50" s="10" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="51" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="11" t="s">
+    <row r="51" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="10" t="s">
         <v>493</v>
       </c>
-      <c r="C51" s="11">
+      <c r="C51" s="10">
         <v>400</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="E51" s="11">
-        <v>1</v>
-      </c>
-      <c r="F51" s="11" t="s">
+      <c r="E51" s="10">
+        <v>1</v>
+      </c>
+      <c r="F51" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="G51" s="11" t="b">
+      <c r="G51" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H51" s="11" t="s">
+      <c r="H51" s="10" t="s">
         <v>630</v>
       </c>
-      <c r="I51" s="11" t="s">
+      <c r="I51" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="J51" s="11" t="s">
+      <c r="J51" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="K51" s="11" t="s">
+      <c r="K51" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="L51" s="11" t="s">
+      <c r="L51" s="10" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="11" t="s">
+    <row r="52" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="10" t="s">
         <v>494</v>
       </c>
-      <c r="C52" s="11">
+      <c r="C52" s="10">
         <v>500</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D52" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="E52" s="11">
-        <v>1</v>
-      </c>
-      <c r="F52" s="11" t="s">
+      <c r="E52" s="10">
+        <v>1</v>
+      </c>
+      <c r="F52" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="G52" s="11" t="b">
+      <c r="G52" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H52" s="11" t="s">
+      <c r="H52" s="10" t="s">
         <v>635</v>
       </c>
-      <c r="I52" s="11" t="s">
+      <c r="I52" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="J52" s="11" t="s">
+      <c r="J52" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="K52" s="11" t="s">
+      <c r="K52" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="L52" s="11" t="s">
+      <c r="L52" s="10" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="53" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="11" t="s">
+    <row r="53" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="C53" s="11">
+      <c r="C53" s="10">
         <v>300</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="E53" s="11">
-        <v>1</v>
-      </c>
-      <c r="F53" s="11" t="s">
+      <c r="E53" s="10">
+        <v>1</v>
+      </c>
+      <c r="F53" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="G53" s="11" t="b">
+      <c r="G53" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H53" s="11" t="s">
+      <c r="H53" s="10" t="s">
         <v>636</v>
       </c>
-      <c r="I53" s="11" t="s">
+      <c r="I53" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="J53" s="11" t="s">
+      <c r="J53" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="K53" s="11" t="s">
+      <c r="K53" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="L53" s="11" t="s">
+      <c r="L53" s="10" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="54" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="11" t="s">
+    <row r="54" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="C54" s="11">
+      <c r="C54" s="10">
         <v>30</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D54" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="E54" s="11">
-        <v>1</v>
-      </c>
-      <c r="F54" s="11" t="s">
+      <c r="E54" s="10">
+        <v>1</v>
+      </c>
+      <c r="F54" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="G54" s="11" t="b">
+      <c r="G54" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H54" s="10" t="s">
         <v>637</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="I54" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="J54" s="11" t="s">
+      <c r="J54" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="K54" s="11" t="s">
+      <c r="K54" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="L54" s="11" t="s">
+      <c r="L54" s="10" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="55" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="11" t="s">
+    <row r="55" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="10" t="s">
         <v>497</v>
       </c>
-      <c r="C55" s="11">
+      <c r="C55" s="10">
         <v>300</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="E55" s="11">
-        <v>1</v>
-      </c>
-      <c r="F55" s="11" t="s">
+      <c r="E55" s="10">
+        <v>1</v>
+      </c>
+      <c r="F55" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="G55" s="11" t="b">
+      <c r="G55" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H55" s="11" t="s">
+      <c r="H55" s="10" t="s">
         <v>638</v>
       </c>
-      <c r="I55" s="11" t="s">
+      <c r="I55" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="J55" s="11" t="s">
+      <c r="J55" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="K55" s="11" t="s">
+      <c r="K55" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="L55" s="11" t="s">
+      <c r="L55" s="10" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="56" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="11" t="s">
+    <row r="56" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="10" t="s">
         <v>498</v>
       </c>
-      <c r="C56" s="11">
+      <c r="C56" s="10">
         <v>300</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="10" t="s">
         <v>591</v>
       </c>
-      <c r="E56" s="11">
-        <v>1</v>
-      </c>
-      <c r="F56" s="11" t="s">
+      <c r="E56" s="10">
+        <v>1</v>
+      </c>
+      <c r="F56" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="G56" s="11" t="b">
+      <c r="G56" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H56" s="11" t="s">
+      <c r="H56" s="10" t="s">
         <v>639</v>
       </c>
-      <c r="I56" s="11" t="s">
+      <c r="I56" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="J56" s="11" t="s">
+      <c r="J56" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="K56" s="11" t="s">
+      <c r="K56" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="L56" s="11" t="s">
+      <c r="L56" s="10" t="s">
         <v>699</v>
       </c>
     </row>
@@ -19496,41 +19504,41 @@
         <v>706</v>
       </c>
     </row>
-    <row r="78" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="5" t="s">
+    <row r="78" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="11" t="s">
         <v>517</v>
       </c>
-      <c r="C78" s="5">
-        <v>-130</v>
-      </c>
-      <c r="D78" s="5" t="s">
+      <c r="C78" s="11">
+        <v>-1500</v>
+      </c>
+      <c r="D78" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="E78" s="5">
-        <v>1</v>
-      </c>
-      <c r="F78" s="5" t="s">
+      <c r="E78" s="11">
+        <v>1</v>
+      </c>
+      <c r="F78" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="G78" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H78" s="5" t="s">
+      <c r="G78" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H78" s="11" t="s">
         <v>653</v>
       </c>
-      <c r="I78" s="5" t="s">
+      <c r="I78" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="J78" s="5" t="s">
+      <c r="J78" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="K78" s="5" t="s">
+      <c r="K78" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="L78" s="5" t="s">
+      <c r="L78" s="11" t="s">
         <v>707</v>
       </c>
     </row>
@@ -19954,79 +19962,79 @@
         <v>709</v>
       </c>
     </row>
-    <row r="90" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="6" t="s">
+    <row r="90" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="C90" s="6">
+      <c r="C90" s="5">
         <v>-20</v>
       </c>
-      <c r="D90" s="6" t="s">
+      <c r="D90" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="E90" s="6">
-        <v>1</v>
-      </c>
-      <c r="F90" s="6" t="s">
+      <c r="E90" s="5">
+        <v>1</v>
+      </c>
+      <c r="F90" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="G90" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H90" s="6" t="s">
+      <c r="G90" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H90" s="5" t="s">
         <v>662</v>
       </c>
-      <c r="I90" s="6" t="s">
+      <c r="I90" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="J90" s="6" t="s">
+      <c r="J90" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="K90" s="6" t="s">
+      <c r="K90" s="5" t="s">
         <v>688</v>
       </c>
-      <c r="L90" s="6" t="s">
+      <c r="L90" s="5" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="91" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="6" t="s">
+    <row r="91" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="C91" s="6">
+      <c r="C91" s="5">
         <v>-20</v>
       </c>
-      <c r="D91" s="6" t="s">
+      <c r="D91" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="E91" s="6">
-        <v>1</v>
-      </c>
-      <c r="F91" s="6" t="s">
+      <c r="E91" s="5">
+        <v>1</v>
+      </c>
+      <c r="F91" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="G91" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H91" s="6" t="s">
+      <c r="G91" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H91" s="5" t="s">
         <v>662</v>
       </c>
-      <c r="I91" s="6" t="s">
+      <c r="I91" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="J91" s="6" t="s">
+      <c r="J91" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="K91" s="6" t="s">
+      <c r="K91" s="5" t="s">
         <v>688</v>
       </c>
-      <c r="L91" s="6" t="s">
+      <c r="L91" s="5" t="s">
         <v>710</v>
       </c>
     </row>
@@ -20069,42 +20077,42 @@
         <v>710</v>
       </c>
     </row>
-    <row r="93" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="6" t="s">
+    <row r="93" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B93" s="6" t="s">
+      <c r="B93" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="C93" s="6">
+      <c r="C93" s="5">
         <f>-20.0067</f>
         <v>-20.006699999999999</v>
       </c>
-      <c r="D93" s="6" t="s">
+      <c r="D93" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="E93" s="6">
-        <v>1</v>
-      </c>
-      <c r="F93" s="6" t="s">
+      <c r="E93" s="5">
+        <v>1</v>
+      </c>
+      <c r="F93" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="G93" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H93" s="6" t="s">
+      <c r="G93" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H93" s="5" t="s">
         <v>662</v>
       </c>
-      <c r="I93" s="6" t="s">
+      <c r="I93" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="J93" s="6" t="s">
+      <c r="J93" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="K93" s="6" t="s">
+      <c r="K93" s="5" t="s">
         <v>688</v>
       </c>
-      <c r="L93" s="6" t="s">
+      <c r="L93" s="5" t="s">
         <v>710</v>
       </c>
     </row>
@@ -20186,41 +20194,41 @@
         <v>710</v>
       </c>
     </row>
-    <row r="96" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="6" t="s">
+    <row r="96" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B96" s="6" t="s">
+      <c r="B96" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="C96" s="6">
+      <c r="C96" s="5">
         <v>-10000</v>
       </c>
-      <c r="D96" s="6" t="s">
+      <c r="D96" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="E96" s="6">
-        <v>1</v>
-      </c>
-      <c r="F96" s="6" t="s">
+      <c r="E96" s="5">
+        <v>1</v>
+      </c>
+      <c r="F96" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="G96" s="6" t="b">
+      <c r="G96" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="H96" s="6" t="s">
+      <c r="H96" s="5" t="s">
         <v>663</v>
       </c>
-      <c r="I96" s="6" t="s">
+      <c r="I96" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="J96" s="6" t="s">
+      <c r="J96" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="K96" s="6" t="s">
+      <c r="K96" s="5" t="s">
         <v>688</v>
       </c>
-      <c r="L96" s="6" t="s">
+      <c r="L96" s="5" t="s">
         <v>711</v>
       </c>
     </row>
@@ -22678,7 +22686,7 @@
     <col min="6" max="6" width="26.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="37.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="84.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="9" bestFit="1" customWidth="1"/>
@@ -23813,50 +23821,50 @@
         <v>824</v>
       </c>
     </row>
-    <row r="25" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="9" t="s">
+    <row r="25" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="8" t="s">
         <v>2046</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="C25" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="D25" s="9">
+      <c r="C25" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="8">
         <v>99</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="8" t="s">
         <v>767</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="8" t="s">
         <v>2047</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="8">
         <v>5</v>
       </c>
-      <c r="J25" s="9" t="s">
+      <c r="J25" s="8" t="s">
         <v>797</v>
       </c>
-      <c r="K25" s="9">
-        <v>1</v>
-      </c>
-      <c r="L25" s="9" t="s">
+      <c r="K25" s="8">
+        <v>1</v>
+      </c>
+      <c r="L25" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="M25" s="9">
+      <c r="M25" s="8">
         <v>99</v>
       </c>
-      <c r="N25" s="9" t="b">
+      <c r="N25" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="O25" s="9" t="s">
+      <c r="O25" s="8" t="s">
         <v>825</v>
       </c>
     </row>
@@ -23907,97 +23915,97 @@
         <v>826</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+    <row r="27" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="11" t="s">
         <v>739</v>
       </c>
-      <c r="C27" t="b">
-        <v>1</v>
-      </c>
-      <c r="D27">
+      <c r="C27" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" s="11">
         <v>99</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="11" t="s">
         <v>765</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="11" t="s">
         <v>785</v>
       </c>
-      <c r="I27">
-        <v>13000000</v>
-      </c>
-      <c r="J27" t="s">
+      <c r="I27" s="11">
+        <v>30000000</v>
+      </c>
+      <c r="J27" s="11" t="s">
         <v>798</v>
       </c>
-      <c r="K27">
-        <v>1</v>
-      </c>
-      <c r="L27" t="s">
+      <c r="K27" s="11">
+        <v>1</v>
+      </c>
+      <c r="L27" s="11" t="s">
         <v>806</v>
       </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-      <c r="N27" t="b">
-        <v>1</v>
-      </c>
-      <c r="O27" t="s">
+      <c r="M27" s="11">
+        <v>1</v>
+      </c>
+      <c r="N27" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O27" s="11" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="28" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="6" t="s">
         <v>740</v>
       </c>
-      <c r="C28" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="D28" s="7">
+      <c r="C28" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D28" s="6">
         <v>99</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="6" t="s">
         <v>765</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="H28" s="6" t="s">
         <v>786</v>
       </c>
-      <c r="I28" s="7">
+      <c r="I28" s="6">
         <v>15000000</v>
       </c>
-      <c r="J28" s="7" t="s">
+      <c r="J28" s="6" t="s">
         <v>798</v>
       </c>
-      <c r="K28" s="7">
-        <v>1</v>
-      </c>
-      <c r="L28" s="7" t="s">
+      <c r="K28" s="6">
+        <v>1</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>2048</v>
       </c>
-      <c r="M28" s="7">
-        <v>1</v>
-      </c>
-      <c r="N28" s="7" t="b">
+      <c r="M28" s="6">
+        <v>1</v>
+      </c>
+      <c r="N28" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O28" s="7" t="s">
+      <c r="O28" s="6" t="s">
         <v>826</v>
       </c>
     </row>
@@ -24189,50 +24197,50 @@
         <v>828</v>
       </c>
     </row>
-    <row r="33" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="13" t="s">
         <v>745</v>
       </c>
-      <c r="C33" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D33" s="6">
+      <c r="C33" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13">
         <v>99</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="13" t="s">
         <v>770</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="H33" s="13" t="s">
         <v>790</v>
       </c>
-      <c r="I33" s="6">
-        <v>-70</v>
-      </c>
-      <c r="J33" s="6" t="s">
+      <c r="I33" s="13">
+        <v>-300</v>
+      </c>
+      <c r="J33" s="13" t="s">
         <v>800</v>
       </c>
-      <c r="K33" s="6">
-        <v>1</v>
-      </c>
-      <c r="L33" s="6" t="s">
+      <c r="K33" s="13">
+        <v>1</v>
+      </c>
+      <c r="L33" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="M33" s="6">
+      <c r="M33" s="13">
         <v>99</v>
       </c>
-      <c r="N33" s="6" t="b">
+      <c r="N33" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="O33" s="6" t="s">
+      <c r="O33" s="13" t="s">
         <v>829</v>
       </c>
     </row>
@@ -24331,144 +24339,144 @@
         <v>831</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
+    <row r="36" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="11" t="s">
         <v>747</v>
       </c>
-      <c r="C36" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D36" s="6">
+      <c r="C36" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D36" s="11">
         <v>99</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F36" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="11" t="s">
         <v>771</v>
       </c>
-      <c r="H36" s="6" t="s">
+      <c r="H36" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="I36" s="6">
-        <v>-20</v>
-      </c>
-      <c r="J36" s="6" t="s">
+      <c r="I36" s="11">
+        <v>-27</v>
+      </c>
+      <c r="J36" s="11" t="s">
         <v>590</v>
       </c>
-      <c r="K36" s="6">
-        <v>1</v>
-      </c>
-      <c r="L36" s="6" t="s">
+      <c r="K36" s="11">
+        <v>1</v>
+      </c>
+      <c r="L36" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="M36" s="6">
+      <c r="M36" s="11">
         <v>99</v>
       </c>
-      <c r="N36" s="6" t="b">
+      <c r="N36" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="O36" s="6" t="s">
+      <c r="O36" s="11" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+    <row r="37" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="11" t="s">
         <v>748</v>
       </c>
-      <c r="C37" t="b">
-        <v>1</v>
-      </c>
-      <c r="D37">
+      <c r="C37" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D37" s="11">
         <v>99</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="11" t="s">
         <v>772</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37" s="11" t="s">
         <v>792</v>
       </c>
-      <c r="I37">
-        <v>-31</v>
-      </c>
-      <c r="J37" t="s">
+      <c r="I37" s="11">
+        <v>-120</v>
+      </c>
+      <c r="J37" s="11" t="s">
         <v>801</v>
       </c>
-      <c r="K37">
-        <v>1</v>
-      </c>
-      <c r="L37" t="s">
+      <c r="K37" s="11">
+        <v>1</v>
+      </c>
+      <c r="L37" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="M37">
+      <c r="M37" s="11">
         <v>99</v>
       </c>
-      <c r="N37" t="b">
+      <c r="N37" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="O37" t="s">
+      <c r="O37" s="11" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="38" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
+    <row r="38" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="C38" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D38" s="6">
+      <c r="C38" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D38" s="5">
         <v>99</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" s="5" t="s">
         <v>760</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="5" t="s">
         <v>762</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="5" t="s">
         <v>763</v>
       </c>
-      <c r="H38" s="6" t="s">
+      <c r="H38" s="5" t="s">
         <v>793</v>
       </c>
-      <c r="I38" s="6">
+      <c r="I38" s="5">
         <v>-19</v>
       </c>
-      <c r="J38" s="6" t="s">
+      <c r="J38" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="K38" s="6">
-        <v>1</v>
-      </c>
-      <c r="L38" s="6" t="s">
+      <c r="K38" s="5">
+        <v>1</v>
+      </c>
+      <c r="L38" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="M38" s="6">
+      <c r="M38" s="5">
         <v>99</v>
       </c>
-      <c r="N38" s="6" t="b">
+      <c r="N38" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="O38" s="6" t="s">
+      <c r="O38" s="5" t="s">
         <v>834</v>
       </c>
     </row>
@@ -24801,97 +24809,97 @@
         <v>838</v>
       </c>
     </row>
-    <row r="46" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
+    <row r="46" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="11" t="s">
         <v>1887</v>
       </c>
-      <c r="C46" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D46" s="6">
+      <c r="C46" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D46" s="11">
         <v>99</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="11" t="s">
         <v>760</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="11" t="s">
         <v>762</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="G46" s="11" t="s">
         <v>763</v>
       </c>
-      <c r="H46" s="6" t="s">
+      <c r="H46" s="11" t="s">
         <v>459</v>
       </c>
-      <c r="I46" s="6">
-        <v>-81</v>
-      </c>
-      <c r="J46" s="6" t="s">
+      <c r="I46" s="11">
+        <v>-293</v>
+      </c>
+      <c r="J46" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="K46" s="6">
-        <v>1</v>
-      </c>
-      <c r="L46" s="6" t="s">
+      <c r="K46" s="11">
+        <v>1</v>
+      </c>
+      <c r="L46" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="M46" s="6">
+      <c r="M46" s="11">
         <v>99</v>
       </c>
-      <c r="N46" s="6" t="b">
+      <c r="N46" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="O46" s="6" t="s">
+      <c r="O46" s="11" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="47" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="9" t="s">
+    <row r="47" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="8" t="s">
         <v>756</v>
       </c>
-      <c r="C47" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="D47" s="9">
+      <c r="C47" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D47" s="8">
         <v>99</v>
       </c>
-      <c r="E47" s="9" t="s">
+      <c r="E47" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="G47" s="8" t="s">
         <v>775</v>
       </c>
-      <c r="H47" s="9" t="s">
+      <c r="H47" s="8" t="s">
         <v>505</v>
       </c>
-      <c r="I47" s="9">
+      <c r="I47" s="8">
         <v>0</v>
       </c>
-      <c r="J47" s="9" t="s">
+      <c r="J47" s="8" t="s">
         <v>593</v>
       </c>
-      <c r="K47" s="9">
+      <c r="K47" s="8">
         <v>0</v>
       </c>
-      <c r="L47" s="9" t="s">
+      <c r="L47" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="M47" s="9">
+      <c r="M47" s="8">
         <v>99</v>
       </c>
-      <c r="N47" s="9" t="b">
+      <c r="N47" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="O47" s="9" t="s">
+      <c r="O47" s="8" t="s">
         <v>839</v>
       </c>
     </row>
@@ -24989,238 +24997,238 @@
         <v>841</v>
       </c>
     </row>
-    <row r="50" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="9" t="s">
+    <row r="50" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="11" t="s">
         <v>2038</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="11" t="s">
         <v>758</v>
       </c>
-      <c r="C50" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="D50" s="9">
+      <c r="C50" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D50" s="11">
         <v>99</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E50" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F50" s="9" t="s">
+      <c r="F50" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="G50" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="H50" s="9" t="s">
+      <c r="H50" s="11" t="s">
         <v>2041</v>
       </c>
-      <c r="I50" s="9">
-        <v>-10</v>
-      </c>
-      <c r="J50" s="9" t="s">
+      <c r="I50" s="11">
+        <v>-20</v>
+      </c>
+      <c r="J50" s="11" t="s">
         <v>804</v>
       </c>
-      <c r="K50" s="9">
-        <v>1</v>
-      </c>
-      <c r="L50" s="9" t="s">
+      <c r="K50" s="11">
+        <v>1</v>
+      </c>
+      <c r="L50" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="M50" s="9">
+      <c r="M50" s="11">
         <v>99</v>
       </c>
-      <c r="N50" s="9" t="b">
+      <c r="N50" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="O50" s="9" t="s">
+      <c r="O50" s="11" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="51" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="9" t="s">
+    <row r="51" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="11" t="s">
         <v>2039</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="11" t="s">
         <v>1891</v>
       </c>
-      <c r="C51" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="D51" s="9">
+      <c r="C51" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D51" s="11">
         <v>99</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="E51" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="F51" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="G51" s="9" t="s">
+      <c r="G51" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="H51" s="9" t="s">
+      <c r="H51" s="11" t="s">
         <v>480</v>
       </c>
-      <c r="I51" s="9">
-        <v>-0.2</v>
-      </c>
-      <c r="J51" s="9" t="s">
+      <c r="I51" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J51" s="11" t="s">
         <v>804</v>
       </c>
-      <c r="K51" s="9">
-        <v>1</v>
-      </c>
-      <c r="L51" s="9" t="s">
+      <c r="K51" s="11">
+        <v>1</v>
+      </c>
+      <c r="L51" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="M51" s="9">
+      <c r="M51" s="11">
         <v>99</v>
       </c>
-      <c r="N51" s="9" t="b">
+      <c r="N51" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="O51" s="9" t="s">
+      <c r="O51" s="11" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="52" spans="1:15" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="9" t="s">
+    <row r="52" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="11" t="s">
         <v>2040</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="11" t="s">
         <v>1890</v>
       </c>
-      <c r="C52" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="D52" s="9">
+      <c r="C52" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D52" s="11">
         <v>99</v>
       </c>
-      <c r="E52" s="9" t="s">
+      <c r="E52" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="F52" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="G52" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="H52" s="9" t="s">
+      <c r="H52" s="11" t="s">
         <v>2042</v>
       </c>
-      <c r="I52" s="9">
-        <v>-0.3</v>
-      </c>
-      <c r="J52" s="9" t="s">
+      <c r="I52" s="11">
+        <v>-8</v>
+      </c>
+      <c r="J52" s="11" t="s">
         <v>804</v>
       </c>
-      <c r="K52" s="9">
-        <v>1</v>
-      </c>
-      <c r="L52" s="9" t="s">
+      <c r="K52" s="11">
+        <v>1</v>
+      </c>
+      <c r="L52" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="M52" s="9">
+      <c r="M52" s="11">
         <v>99</v>
       </c>
-      <c r="N52" s="9" t="b">
+      <c r="N52" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="O52" s="9" t="s">
+      <c r="O52" s="11" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A53" s="6" t="s">
+    <row r="53" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="11" t="s">
         <v>2049</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="11" t="s">
         <v>1889</v>
       </c>
-      <c r="C53" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D53" s="6">
+      <c r="C53" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D53" s="11">
         <v>99</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E53" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F53" s="6" t="s">
+      <c r="F53" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="G53" s="6" t="s">
+      <c r="G53" s="11" t="s">
         <v>763</v>
       </c>
-      <c r="H53" s="6" t="s">
+      <c r="H53" s="11" t="s">
         <v>2058</v>
       </c>
-      <c r="I53" s="6">
-        <v>20000000</v>
-      </c>
-      <c r="J53" s="6" t="s">
+      <c r="I53" s="11">
+        <v>200000000</v>
+      </c>
+      <c r="J53" s="11" t="s">
         <v>2051</v>
       </c>
-      <c r="K53" s="6">
-        <v>1</v>
-      </c>
-      <c r="L53" s="6" t="s">
+      <c r="K53" s="11">
+        <v>1</v>
+      </c>
+      <c r="L53" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="M53" s="6">
+      <c r="M53" s="11">
         <v>99</v>
       </c>
-      <c r="N53" s="6" t="b">
+      <c r="N53" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="O53" s="6" t="s">
+      <c r="O53" s="11" t="s">
         <v>2052</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="5" t="s">
         <v>2050</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="5" t="s">
         <v>1901</v>
       </c>
-      <c r="C54" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D54" s="6">
+      <c r="C54" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D54" s="5">
         <v>99</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E54" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F54" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="G54" s="6" t="s">
+      <c r="G54" s="5" t="s">
         <v>763</v>
       </c>
-      <c r="H54" s="6" t="s">
+      <c r="H54" s="5" t="s">
         <v>2057</v>
       </c>
-      <c r="I54" s="6">
+      <c r="I54" s="5">
         <v>7500000</v>
       </c>
-      <c r="J54" s="6" t="s">
+      <c r="J54" s="5" t="s">
         <v>2051</v>
       </c>
-      <c r="K54" s="6">
-        <v>1</v>
-      </c>
-      <c r="L54" s="6" t="s">
+      <c r="K54" s="5">
+        <v>1</v>
+      </c>
+      <c r="L54" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="M54" s="6">
+      <c r="M54" s="5">
         <v>99</v>
       </c>
-      <c r="N54" s="6" t="b">
+      <c r="N54" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="O54" s="6" t="s">
+      <c r="O54" s="5" t="s">
         <v>2053</v>
       </c>
     </row>
@@ -26390,35 +26398,35 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
         <v>505</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>-140</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>593</v>
       </c>
-      <c r="D2" s="10">
-        <v>1</v>
-      </c>
-      <c r="E2" s="10" t="s">
+      <c r="D2" s="9">
+        <v>1</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>886</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>890</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="9">
         <v>0</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="9" t="s">
         <v>895</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="9" t="s">
         <v>351</v>
       </c>
     </row>
@@ -26454,35 +26462,35 @@
         <v>351</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <v>-140</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>593</v>
       </c>
-      <c r="D4" s="10">
-        <v>1</v>
-      </c>
-      <c r="E4" s="10" t="s">
+      <c r="D4" s="9">
+        <v>1</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>888</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>892</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>0</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>2059</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="9" t="s">
         <v>351</v>
       </c>
     </row>
